--- a/analysis/edcr/out/top_f1/nickel_shift_new_20_results.xlsx
+++ b/analysis/edcr/out/top_f1/nickel_shift_new_20_results.xlsx
@@ -552,7 +552,7 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E2">
         <v>0.5918367346938775</v>
@@ -576,31 +576,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L2">
-        <v>0.6078431372549019</v>
+        <v>0.5625</v>
       </c>
       <c r="M2">
-        <v>0.5081967213114754</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="N2">
-        <v>0.5535714285714285</v>
+        <v>0.576</v>
       </c>
       <c r="O2">
-        <v>0.01600640256102437</v>
+        <v>-0.02933673469387754</v>
       </c>
       <c r="P2">
-        <v>0.03278688524590173</v>
+        <v>0.1147540983606558</v>
       </c>
       <c r="Q2">
-        <v>0.02629870129870115</v>
+        <v>0.04872727272727262</v>
       </c>
       <c r="R2">
-        <v>0.02704530087897221</v>
+        <v>-0.04956896551724137</v>
       </c>
       <c r="S2">
-        <v>0.06896551724137952</v>
+        <v>0.2413793103448278</v>
       </c>
       <c r="T2">
-        <v>0.04987684729064012</v>
+        <v>0.09241379310344806</v>
       </c>
       <c r="U2" t="s">
         <v>31</v>
@@ -617,7 +617,7 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E3">
         <v>0.5918367346938775</v>
@@ -641,31 +641,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L3">
-        <v>0.6078431372549019</v>
+        <v>0.5625</v>
       </c>
       <c r="M3">
-        <v>0.5081967213114754</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="N3">
-        <v>0.5535714285714285</v>
+        <v>0.576</v>
       </c>
       <c r="O3">
-        <v>0.01600640256102437</v>
+        <v>-0.02933673469387754</v>
       </c>
       <c r="P3">
-        <v>0.03278688524590173</v>
+        <v>0.1147540983606558</v>
       </c>
       <c r="Q3">
-        <v>0.02629870129870115</v>
+        <v>0.04872727272727262</v>
       </c>
       <c r="R3">
-        <v>0.02704530087897221</v>
+        <v>-0.04956896551724137</v>
       </c>
       <c r="S3">
-        <v>0.06896551724137952</v>
+        <v>0.2413793103448278</v>
       </c>
       <c r="T3">
-        <v>0.04987684729064012</v>
+        <v>0.09241379310344806</v>
       </c>
       <c r="U3" t="s">
         <v>31</v>
@@ -682,7 +682,7 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E4">
         <v>0.5918367346938775</v>
@@ -747,7 +747,7 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E5">
         <v>0.5918367346938775</v>
@@ -771,31 +771,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L5">
-        <v>0.5769230769230769</v>
+        <v>0.6</v>
       </c>
       <c r="M5">
         <v>0.4918032786885246</v>
       </c>
       <c r="N5">
-        <v>0.5309734513274337</v>
+        <v>0.5405405405405406</v>
       </c>
       <c r="O5">
-        <v>-0.01491365777080067</v>
+        <v>0.008163265306122436</v>
       </c>
       <c r="P5">
         <v>0.01639344262295089</v>
       </c>
       <c r="Q5">
-        <v>0.003700724054706339</v>
+        <v>0.01326781326781323</v>
       </c>
       <c r="R5">
-        <v>-0.02519893899204251</v>
+        <v>0.01379310344827584</v>
       </c>
       <c r="S5">
         <v>0.03448275862068981</v>
       </c>
       <c r="T5">
-        <v>0.007018614586512022</v>
+        <v>0.0251630941286113</v>
       </c>
       <c r="U5" t="s">
         <v>31</v>
@@ -812,7 +812,7 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E6">
         <v>0.5918367346938775</v>
@@ -836,31 +836,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L6">
-        <v>0.5769230769230769</v>
+        <v>0.5625</v>
       </c>
       <c r="M6">
-        <v>0.4918032786885246</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="N6">
-        <v>0.5309734513274337</v>
+        <v>0.576</v>
       </c>
       <c r="O6">
-        <v>-0.01491365777080067</v>
+        <v>-0.02933673469387754</v>
       </c>
       <c r="P6">
-        <v>0.01639344262295089</v>
+        <v>0.1147540983606558</v>
       </c>
       <c r="Q6">
-        <v>0.003700724054706339</v>
+        <v>0.04872727272727262</v>
       </c>
       <c r="R6">
-        <v>-0.02519893899204251</v>
+        <v>-0.04956896551724137</v>
       </c>
       <c r="S6">
-        <v>0.03448275862068981</v>
+        <v>0.2413793103448278</v>
       </c>
       <c r="T6">
-        <v>0.007018614586512022</v>
+        <v>0.09241379310344806</v>
       </c>
       <c r="U6" t="s">
         <v>31</v>
@@ -874,7 +874,7 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E7">
         <v>0.5918367346938775</v>
@@ -898,31 +898,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L7">
-        <v>0.603448275862069</v>
+        <v>0.6</v>
       </c>
       <c r="M7">
-        <v>0.5737704918032787</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="N7">
-        <v>0.588235294117647</v>
+        <v>0.5950413223140496</v>
       </c>
       <c r="O7">
-        <v>0.01161154116819141</v>
+        <v>0.008163265306122436</v>
       </c>
       <c r="P7">
-        <v>0.09836065573770497</v>
+        <v>0.1147540983606558</v>
       </c>
       <c r="Q7">
-        <v>0.06096256684491963</v>
+        <v>0.06776859504132227</v>
       </c>
       <c r="R7">
-        <v>0.01961950059453031</v>
+        <v>0.01379310344827584</v>
       </c>
       <c r="S7">
-        <v>0.2068965517241381</v>
+        <v>0.2413793103448278</v>
       </c>
       <c r="T7">
-        <v>0.1156186612576062</v>
+        <v>0.128526645768025</v>
       </c>
       <c r="U7" t="s">
         <v>31</v>
@@ -939,7 +939,7 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>0.5918367346938775</v>
@@ -963,31 +963,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L8">
-        <v>0.6071428571428571</v>
+        <v>0.603448275862069</v>
       </c>
       <c r="M8">
-        <v>0.5573770491803278</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="N8">
-        <v>0.5811965811965811</v>
+        <v>0.588235294117647</v>
       </c>
       <c r="O8">
-        <v>0.01530612244897955</v>
+        <v>0.01161154116819141</v>
       </c>
       <c r="P8">
-        <v>0.08196721311475413</v>
+        <v>0.09836065573770497</v>
       </c>
       <c r="Q8">
-        <v>0.05392385392385379</v>
+        <v>0.06096256684491963</v>
       </c>
       <c r="R8">
-        <v>0.02586206896551718</v>
+        <v>0.01961950059453031</v>
       </c>
       <c r="S8">
-        <v>0.1724137931034484</v>
+        <v>0.2068965517241381</v>
       </c>
       <c r="T8">
-        <v>0.1022693781314468</v>
+        <v>0.1156186612576062</v>
       </c>
       <c r="U8" t="s">
         <v>31</v>
@@ -1004,7 +1004,7 @@
         <v>30</v>
       </c>
       <c r="D9">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E9">
         <v>0.5918367346938775</v>
@@ -1069,7 +1069,7 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E10">
         <v>0.5918367346938775</v>
@@ -1134,7 +1134,7 @@
         <v>30</v>
       </c>
       <c r="D11">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E11">
         <v>0.5918367346938775</v>
@@ -1158,31 +1158,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L11">
-        <v>0.603448275862069</v>
+        <v>0.6</v>
       </c>
       <c r="M11">
-        <v>0.5737704918032787</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="N11">
-        <v>0.588235294117647</v>
+        <v>0.5950413223140496</v>
       </c>
       <c r="O11">
-        <v>0.01161154116819141</v>
+        <v>0.008163265306122436</v>
       </c>
       <c r="P11">
-        <v>0.09836065573770497</v>
+        <v>0.1147540983606558</v>
       </c>
       <c r="Q11">
-        <v>0.06096256684491963</v>
+        <v>0.06776859504132227</v>
       </c>
       <c r="R11">
-        <v>0.01961950059453031</v>
+        <v>0.01379310344827584</v>
       </c>
       <c r="S11">
-        <v>0.2068965517241381</v>
+        <v>0.2413793103448278</v>
       </c>
       <c r="T11">
-        <v>0.1156186612576062</v>
+        <v>0.128526645768025</v>
       </c>
       <c r="U11" t="s">
         <v>31</v>
@@ -1196,7 +1196,7 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>0.3723404255319149</v>
@@ -1220,31 +1220,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L12">
-        <v>0.3760683760683761</v>
+        <v>0.3739130434782609</v>
       </c>
       <c r="M12">
-        <v>0.7213114754098361</v>
+        <v>0.7049180327868853</v>
       </c>
       <c r="N12">
-        <v>0.4943820224719102</v>
+        <v>0.4886363636363636</v>
       </c>
       <c r="O12">
-        <v>0.003727950536461189</v>
+        <v>0.001572617946346</v>
       </c>
       <c r="P12">
-        <v>0.1475409836065574</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="Q12">
-        <v>0.04276911924610377</v>
+        <v>0.03702346041055726</v>
       </c>
       <c r="R12">
-        <v>0.01001221001221005</v>
+        <v>0.004223602484472114</v>
       </c>
       <c r="S12">
-        <v>0.2571428571428572</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="T12">
-        <v>0.09470304975922979</v>
+        <v>0.08198051948051967</v>
       </c>
       <c r="U12" t="s">
         <v>32</v>
@@ -1261,7 +1261,7 @@
         <v>29</v>
       </c>
       <c r="D13">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E13">
         <v>0.3723404255319149</v>
@@ -1285,31 +1285,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L13">
-        <v>0.3760683760683761</v>
+        <v>0.3739130434782609</v>
       </c>
       <c r="M13">
-        <v>0.7213114754098361</v>
+        <v>0.7049180327868853</v>
       </c>
       <c r="N13">
-        <v>0.4943820224719102</v>
+        <v>0.4886363636363636</v>
       </c>
       <c r="O13">
-        <v>0.003727950536461189</v>
+        <v>0.001572617946346</v>
       </c>
       <c r="P13">
-        <v>0.1475409836065574</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="Q13">
-        <v>0.04276911924610377</v>
+        <v>0.03702346041055726</v>
       </c>
       <c r="R13">
-        <v>0.01001221001221005</v>
+        <v>0.004223602484472114</v>
       </c>
       <c r="S13">
-        <v>0.2571428571428572</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="T13">
-        <v>0.09470304975922979</v>
+        <v>0.08198051948051967</v>
       </c>
       <c r="U13" t="s">
         <v>32</v>
@@ -1326,7 +1326,7 @@
         <v>29</v>
       </c>
       <c r="D14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E14">
         <v>0.3723404255319149</v>
@@ -1391,7 +1391,7 @@
         <v>29</v>
       </c>
       <c r="D15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E15">
         <v>0.3723404255319149</v>
@@ -1456,7 +1456,7 @@
         <v>29</v>
       </c>
       <c r="D16">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>0.3723404255319149</v>
@@ -1480,31 +1480,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L16">
-        <v>0.3760683760683761</v>
+        <v>0.3739130434782609</v>
       </c>
       <c r="M16">
-        <v>0.7213114754098361</v>
+        <v>0.7049180327868853</v>
       </c>
       <c r="N16">
-        <v>0.4943820224719102</v>
+        <v>0.4886363636363636</v>
       </c>
       <c r="O16">
-        <v>0.003727950536461189</v>
+        <v>0.001572617946346</v>
       </c>
       <c r="P16">
-        <v>0.1475409836065574</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="Q16">
-        <v>0.04276911924610377</v>
+        <v>0.03702346041055726</v>
       </c>
       <c r="R16">
-        <v>0.01001221001221005</v>
+        <v>0.004223602484472114</v>
       </c>
       <c r="S16">
-        <v>0.2571428571428572</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="T16">
-        <v>0.09470304975922979</v>
+        <v>0.08198051948051967</v>
       </c>
       <c r="U16" t="s">
         <v>32</v>
@@ -1518,7 +1518,7 @@
         <v>30</v>
       </c>
       <c r="D17">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>0.3723404255319149</v>
@@ -1542,31 +1542,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L17">
-        <v>0.3793103448275862</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="M17">
-        <v>0.7213114754098361</v>
+        <v>0.6885245901639344</v>
       </c>
       <c r="N17">
-        <v>0.4971751412429378</v>
+        <v>0.502994011976048</v>
       </c>
       <c r="O17">
-        <v>0.006969919295671312</v>
+        <v>0.02388598956242477</v>
       </c>
       <c r="P17">
-        <v>0.1475409836065574</v>
+        <v>0.1147540983606558</v>
       </c>
       <c r="Q17">
-        <v>0.04556223801713144</v>
+        <v>0.0513811087502416</v>
       </c>
       <c r="R17">
-        <v>0.0187192118226601</v>
+        <v>0.06415094339622653</v>
       </c>
       <c r="S17">
-        <v>0.2571428571428572</v>
+        <v>0.2</v>
       </c>
       <c r="T17">
-        <v>0.1008878127522196</v>
+        <v>0.1137724550898207</v>
       </c>
       <c r="U17" t="s">
         <v>32</v>
@@ -1583,7 +1583,7 @@
         <v>30</v>
       </c>
       <c r="D18">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E18">
         <v>0.3723404255319149</v>
@@ -1607,31 +1607,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L18">
-        <v>0.3793103448275862</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="M18">
-        <v>0.7213114754098361</v>
+        <v>0.6885245901639344</v>
       </c>
       <c r="N18">
-        <v>0.4971751412429378</v>
+        <v>0.502994011976048</v>
       </c>
       <c r="O18">
-        <v>0.006969919295671312</v>
+        <v>0.02388598956242477</v>
       </c>
       <c r="P18">
-        <v>0.1475409836065574</v>
+        <v>0.1147540983606558</v>
       </c>
       <c r="Q18">
-        <v>0.04556223801713144</v>
+        <v>0.0513811087502416</v>
       </c>
       <c r="R18">
-        <v>0.0187192118226601</v>
+        <v>0.06415094339622653</v>
       </c>
       <c r="S18">
-        <v>0.2571428571428572</v>
+        <v>0.2</v>
       </c>
       <c r="T18">
-        <v>0.1008878127522196</v>
+        <v>0.1137724550898207</v>
       </c>
       <c r="U18" t="s">
         <v>32</v>
@@ -1648,7 +1648,7 @@
         <v>30</v>
       </c>
       <c r="D19">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E19">
         <v>0.3723404255319149</v>
@@ -1713,7 +1713,7 @@
         <v>30</v>
       </c>
       <c r="D20">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E20">
         <v>0.3723404255319149</v>
@@ -1737,31 +1737,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L20">
-        <v>0.3771929824561404</v>
+        <v>0.3805309734513274</v>
       </c>
       <c r="M20">
         <v>0.7049180327868853</v>
       </c>
       <c r="N20">
-        <v>0.4914285714285714</v>
+        <v>0.4942528735632184</v>
       </c>
       <c r="O20">
-        <v>0.004852556924225482</v>
+        <v>0.008190547919412539</v>
       </c>
       <c r="P20">
         <v>0.1311475409836066</v>
       </c>
       <c r="Q20">
-        <v>0.03981566820276505</v>
+        <v>0.04263997033741201</v>
       </c>
       <c r="R20">
-        <v>0.01303258145363415</v>
+        <v>0.02199747155499368</v>
       </c>
       <c r="S20">
         <v>0.2285714285714286</v>
       </c>
       <c r="T20">
-        <v>0.08816326530612263</v>
+        <v>0.09441707717569804</v>
       </c>
       <c r="U20" t="s">
         <v>32</v>
@@ -1778,7 +1778,7 @@
         <v>30</v>
       </c>
       <c r="D21">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E21">
         <v>0.3723404255319149</v>
@@ -1802,31 +1802,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L21">
-        <v>0.3793103448275862</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="M21">
-        <v>0.7213114754098361</v>
+        <v>0.6885245901639344</v>
       </c>
       <c r="N21">
-        <v>0.4971751412429378</v>
+        <v>0.502994011976048</v>
       </c>
       <c r="O21">
-        <v>0.006969919295671312</v>
+        <v>0.02388598956242477</v>
       </c>
       <c r="P21">
-        <v>0.1475409836065574</v>
+        <v>0.1147540983606558</v>
       </c>
       <c r="Q21">
-        <v>0.04556223801713144</v>
+        <v>0.0513811087502416</v>
       </c>
       <c r="R21">
-        <v>0.0187192118226601</v>
+        <v>0.06415094339622653</v>
       </c>
       <c r="S21">
-        <v>0.2571428571428572</v>
+        <v>0.2</v>
       </c>
       <c r="T21">
-        <v>0.1008878127522196</v>
+        <v>0.1137724550898207</v>
       </c>
       <c r="U21" t="s">
         <v>32</v>
@@ -1840,7 +1840,7 @@
         <v>29</v>
       </c>
       <c r="D22">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E22">
         <v>0.6571428571428571</v>
@@ -1864,31 +1864,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L22">
-        <v>0.6666666666666666</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="M22">
-        <v>0.4918032786885246</v>
+        <v>0.3770491803278688</v>
       </c>
       <c r="N22">
-        <v>0.5660377358490566</v>
+        <v>0.4791666666666666</v>
       </c>
       <c r="O22">
-        <v>0.00952380952380949</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>0.1147540983606558</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>0.08687106918239001</v>
+        <v>5.551115123125783E-17</v>
       </c>
       <c r="R22">
-        <v>0.01449275362318835</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>0.3043478260869566</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>0.1812961443806401</v>
+        <v>1.158493590913207E-16</v>
       </c>
       <c r="U22" t="s">
         <v>33</v>
@@ -1905,7 +1905,7 @@
         <v>29</v>
       </c>
       <c r="D23">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E23">
         <v>0.6571428571428571</v>
@@ -1929,31 +1929,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L23">
-        <v>0.6666666666666666</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="M23">
-        <v>0.4918032786885246</v>
+        <v>0.3770491803278688</v>
       </c>
       <c r="N23">
-        <v>0.5660377358490566</v>
+        <v>0.4791666666666666</v>
       </c>
       <c r="O23">
-        <v>0.00952380952380949</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>0.1147540983606558</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>0.08687106918239001</v>
+        <v>5.551115123125783E-17</v>
       </c>
       <c r="R23">
-        <v>0.01449275362318835</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>0.3043478260869566</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>0.1812961443806401</v>
+        <v>1.158493590913207E-16</v>
       </c>
       <c r="U23" t="s">
         <v>33</v>
@@ -1970,7 +1970,7 @@
         <v>29</v>
       </c>
       <c r="D24">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E24">
         <v>0.6571428571428571</v>
@@ -2035,7 +2035,7 @@
         <v>29</v>
       </c>
       <c r="D25">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E25">
         <v>0.6571428571428571</v>
@@ -2059,31 +2059,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L25">
-        <v>0.6666666666666666</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="M25">
-        <v>0.459016393442623</v>
+        <v>0.3770491803278688</v>
       </c>
       <c r="N25">
-        <v>0.5436893203883496</v>
+        <v>0.4791666666666666</v>
       </c>
       <c r="O25">
-        <v>0.00952380952380949</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>0.08196721311475413</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>0.06452265372168303</v>
+        <v>5.551115123125783E-17</v>
       </c>
       <c r="R25">
-        <v>0.01449275362318835</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>0.2173913043478262</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>0.134655972984382</v>
+        <v>1.158493590913207E-16</v>
       </c>
       <c r="U25" t="s">
         <v>33</v>
@@ -2100,7 +2100,7 @@
         <v>29</v>
       </c>
       <c r="D26">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E26">
         <v>0.6571428571428571</v>
@@ -2124,31 +2124,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L26">
-        <v>0.6666666666666666</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="M26">
-        <v>0.4918032786885246</v>
+        <v>0.3770491803278688</v>
       </c>
       <c r="N26">
-        <v>0.5660377358490566</v>
+        <v>0.4791666666666666</v>
       </c>
       <c r="O26">
-        <v>0.00952380952380949</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>0.1147540983606558</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>0.08687106918239001</v>
+        <v>5.551115123125783E-17</v>
       </c>
       <c r="R26">
-        <v>0.01449275362318835</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>0.3043478260869566</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>0.1812961443806401</v>
+        <v>1.158493590913207E-16</v>
       </c>
       <c r="U26" t="s">
         <v>33</v>
@@ -2162,7 +2162,7 @@
         <v>30</v>
       </c>
       <c r="D27">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E27">
         <v>0.6571428571428571</v>
@@ -2186,31 +2186,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L27">
-        <v>0.6585365853658537</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="M27">
-        <v>0.4426229508196721</v>
+        <v>0.4098360655737705</v>
       </c>
       <c r="N27">
-        <v>0.5294117647058824</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="O27">
-        <v>0.001393728222996549</v>
+        <v>0.01853281853281852</v>
       </c>
       <c r="P27">
-        <v>0.0655737704918033</v>
+        <v>0.03278688524590168</v>
       </c>
       <c r="Q27">
-        <v>0.05024509803921579</v>
+        <v>0.0310374149659865</v>
       </c>
       <c r="R27">
-        <v>0.002120890774125183</v>
+        <v>0.02820211515863687</v>
       </c>
       <c r="S27">
-        <v>0.1739130434782609</v>
+        <v>0.08695652173913054</v>
       </c>
       <c r="T27">
-        <v>0.1048593350383634</v>
+        <v>0.06477373558118922</v>
       </c>
       <c r="U27" t="s">
         <v>33</v>
@@ -2227,7 +2227,7 @@
         <v>30</v>
       </c>
       <c r="D28">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E28">
         <v>0.6571428571428571</v>
@@ -2251,31 +2251,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L28">
-        <v>0.6585365853658537</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="M28">
-        <v>0.4426229508196721</v>
+        <v>0.4262295081967213</v>
       </c>
       <c r="N28">
-        <v>0.5294117647058824</v>
+        <v>0.5252525252525253</v>
       </c>
       <c r="O28">
-        <v>0.001393728222996549</v>
+        <v>0.02706766917293235</v>
       </c>
       <c r="P28">
-        <v>0.0655737704918033</v>
+        <v>0.04918032786885246</v>
       </c>
       <c r="Q28">
-        <v>0.05024509803921579</v>
+        <v>0.04608585858585873</v>
       </c>
       <c r="R28">
-        <v>0.002120890774125183</v>
+        <v>0.04118993135011445</v>
       </c>
       <c r="S28">
-        <v>0.1739130434782609</v>
+        <v>0.1304347826086956</v>
       </c>
       <c r="T28">
-        <v>0.1048593350383634</v>
+        <v>0.0961791831357052</v>
       </c>
       <c r="U28" t="s">
         <v>33</v>
@@ -2292,7 +2292,7 @@
         <v>30</v>
       </c>
       <c r="D29">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E29">
         <v>0.6571428571428571</v>
@@ -2357,7 +2357,7 @@
         <v>30</v>
       </c>
       <c r="D30">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E30">
         <v>0.6571428571428571</v>
@@ -2381,31 +2381,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L30">
-        <v>0.6666666666666666</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="M30">
         <v>0.4262295081967213</v>
       </c>
       <c r="N30">
-        <v>0.52</v>
+        <v>0.5252525252525253</v>
       </c>
       <c r="O30">
-        <v>0.00952380952380949</v>
+        <v>0.02706766917293235</v>
       </c>
       <c r="P30">
         <v>0.04918032786885246</v>
       </c>
       <c r="Q30">
-        <v>0.04083333333333344</v>
+        <v>0.04608585858585873</v>
       </c>
       <c r="R30">
-        <v>0.01449275362318835</v>
+        <v>0.04118993135011445</v>
       </c>
       <c r="S30">
         <v>0.1304347826086956</v>
       </c>
       <c r="T30">
-        <v>0.08521739130434808</v>
+        <v>0.0961791831357052</v>
       </c>
       <c r="U30" t="s">
         <v>33</v>
@@ -2422,7 +2422,7 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E31">
         <v>0.6571428571428571</v>
@@ -2446,31 +2446,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L31">
-        <v>0.6585365853658537</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="M31">
-        <v>0.4426229508196721</v>
+        <v>0.4098360655737705</v>
       </c>
       <c r="N31">
-        <v>0.5294117647058824</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="O31">
-        <v>0.001393728222996549</v>
+        <v>0.01853281853281852</v>
       </c>
       <c r="P31">
-        <v>0.0655737704918033</v>
+        <v>0.03278688524590168</v>
       </c>
       <c r="Q31">
-        <v>0.05024509803921579</v>
+        <v>0.0310374149659865</v>
       </c>
       <c r="R31">
-        <v>0.002120890774125183</v>
+        <v>0.02820211515863687</v>
       </c>
       <c r="S31">
-        <v>0.1739130434782609</v>
+        <v>0.08695652173913054</v>
       </c>
       <c r="T31">
-        <v>0.1048593350383634</v>
+        <v>0.06477373558118922</v>
       </c>
       <c r="U31" t="s">
         <v>33</v>
@@ -2484,7 +2484,7 @@
         <v>29</v>
       </c>
       <c r="D32">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E32">
         <v>0.25</v>
@@ -2508,31 +2508,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L32">
-        <v>0.3</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="M32">
-        <v>0.8360655737704918</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="N32">
-        <v>0.4415584415584415</v>
+        <v>0.5064935064935064</v>
       </c>
       <c r="O32">
-        <v>0.04999999999999999</v>
+        <v>0.1693548387096774</v>
       </c>
       <c r="P32">
-        <v>0.819672131147541</v>
+        <v>0.6229508196721312</v>
       </c>
       <c r="Q32">
-        <v>0.4107892107892108</v>
+        <v>0.4757242757242757</v>
       </c>
       <c r="R32">
-        <v>0.2</v>
+        <v>0.6774193548387097</v>
       </c>
       <c r="S32">
-        <v>50.00000000000006</v>
+        <v>38.00000000000005</v>
       </c>
       <c r="T32">
-        <v>13.35064935064938</v>
+        <v>15.46103896103899</v>
       </c>
       <c r="U32" t="s">
         <v>34</v>
@@ -2549,7 +2549,7 @@
         <v>29</v>
       </c>
       <c r="D33">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E33">
         <v>0.25</v>
@@ -2573,31 +2573,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L33">
-        <v>0.2571428571428571</v>
+        <v>0.3644067796610169</v>
       </c>
       <c r="M33">
-        <v>0.8852459016393442</v>
+        <v>0.7049180327868853</v>
       </c>
       <c r="N33">
-        <v>0.3985239852398523</v>
+        <v>0.4804469273743016</v>
       </c>
       <c r="O33">
-        <v>0.007142857142857117</v>
+        <v>0.1144067796610169</v>
       </c>
       <c r="P33">
-        <v>0.8688524590163934</v>
+        <v>0.6885245901639344</v>
       </c>
       <c r="Q33">
-        <v>0.3677547544706216</v>
+        <v>0.4496776966050709</v>
       </c>
       <c r="R33">
-        <v>0.02857142857142847</v>
+        <v>0.4576271186440677</v>
       </c>
       <c r="S33">
-        <v>53.00000000000006</v>
+        <v>42.00000000000005</v>
       </c>
       <c r="T33">
-        <v>11.95202952029523</v>
+        <v>14.61452513966484</v>
       </c>
       <c r="U33" t="s">
         <v>34</v>
@@ -2614,7 +2614,7 @@
         <v>29</v>
       </c>
       <c r="D34">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E34">
         <v>0.25</v>
@@ -2638,31 +2638,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L34">
-        <v>0.2732558139534884</v>
+        <v>0.4</v>
       </c>
       <c r="M34">
-        <v>0.7704918032786885</v>
+        <v>0.5573770491803278</v>
       </c>
       <c r="N34">
-        <v>0.4034334763948497</v>
+        <v>0.4657534246575343</v>
       </c>
       <c r="O34">
-        <v>0.02325581395348836</v>
+        <v>0.15</v>
       </c>
       <c r="P34">
-        <v>0.7540983606557377</v>
+        <v>0.540983606557377</v>
       </c>
       <c r="Q34">
-        <v>0.372664245625619</v>
+        <v>0.4349841938883036</v>
       </c>
       <c r="R34">
-        <v>0.09302325581395343</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="S34">
-        <v>46.00000000000005</v>
+        <v>33.00000000000004</v>
       </c>
       <c r="T34">
-        <v>12.11158798283264</v>
+        <v>14.1369863013699</v>
       </c>
       <c r="U34" t="s">
         <v>34</v>
@@ -2679,7 +2679,7 @@
         <v>29</v>
       </c>
       <c r="D35">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E35">
         <v>0.25</v>
@@ -2703,31 +2703,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L35">
-        <v>0.3125</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="M35">
-        <v>0.819672131147541</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="N35">
-        <v>0.4524886877828055</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="O35">
-        <v>0.0625</v>
+        <v>0.1686046511627907</v>
       </c>
       <c r="P35">
-        <v>0.8032786885245902</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="Q35">
-        <v>0.4217194570135748</v>
+        <v>0.4590266875981162</v>
       </c>
       <c r="R35">
-        <v>0.25</v>
+        <v>0.6744186046511629</v>
       </c>
       <c r="S35">
-        <v>49.00000000000006</v>
+        <v>35.00000000000004</v>
       </c>
       <c r="T35">
-        <v>13.70588235294121</v>
+        <v>14.91836734693881</v>
       </c>
       <c r="U35" t="s">
         <v>34</v>
@@ -2744,7 +2744,7 @@
         <v>29</v>
       </c>
       <c r="D36">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E36">
         <v>0.25</v>
@@ -2768,31 +2768,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L36">
-        <v>0.3</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="M36">
-        <v>0.8360655737704918</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="N36">
-        <v>0.4415584415584415</v>
+        <v>0.5064935064935064</v>
       </c>
       <c r="O36">
-        <v>0.04999999999999999</v>
+        <v>0.1693548387096774</v>
       </c>
       <c r="P36">
-        <v>0.819672131147541</v>
+        <v>0.6229508196721312</v>
       </c>
       <c r="Q36">
-        <v>0.4107892107892108</v>
+        <v>0.4757242757242757</v>
       </c>
       <c r="R36">
-        <v>0.2</v>
+        <v>0.6774193548387097</v>
       </c>
       <c r="S36">
-        <v>50.00000000000006</v>
+        <v>38.00000000000005</v>
       </c>
       <c r="T36">
-        <v>13.35064935064938</v>
+        <v>15.46103896103899</v>
       </c>
       <c r="U36" t="s">
         <v>34</v>
@@ -2806,7 +2806,7 @@
         <v>30</v>
       </c>
       <c r="D37">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E37">
         <v>0.25</v>
@@ -2830,31 +2830,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L37">
-        <v>0.3309859154929577</v>
+        <v>0.4123711340206185</v>
       </c>
       <c r="M37">
-        <v>0.7704918032786885</v>
+        <v>0.6557377049180327</v>
       </c>
       <c r="N37">
-        <v>0.4630541871921182</v>
+        <v>0.5063291139240507</v>
       </c>
       <c r="O37">
-        <v>0.08098591549295775</v>
+        <v>0.1623711340206185</v>
       </c>
       <c r="P37">
-        <v>0.7540983606557377</v>
+        <v>0.6393442622950819</v>
       </c>
       <c r="Q37">
-        <v>0.4322849564228875</v>
+        <v>0.47555988315482</v>
       </c>
       <c r="R37">
-        <v>0.323943661971831</v>
+        <v>0.6494845360824741</v>
       </c>
       <c r="S37">
-        <v>46.00000000000005</v>
+        <v>39.00000000000004</v>
       </c>
       <c r="T37">
-        <v>14.04926108374388</v>
+        <v>15.45569620253168</v>
       </c>
       <c r="U37" t="s">
         <v>34</v>
@@ -2871,7 +2871,7 @@
         <v>30</v>
       </c>
       <c r="D38">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E38">
         <v>0.25</v>
@@ -2895,31 +2895,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L38">
-        <v>0.2583333333333334</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="M38">
-        <v>0.5081967213114754</v>
+        <v>0.459016393442623</v>
       </c>
       <c r="N38">
-        <v>0.3425414364640884</v>
+        <v>0.3393939393939394</v>
       </c>
       <c r="O38">
-        <v>0.008333333333333359</v>
+        <v>0.01923076923076922</v>
       </c>
       <c r="P38">
-        <v>0.4918032786885246</v>
+        <v>0.4426229508196722</v>
       </c>
       <c r="Q38">
-        <v>0.3117722056948577</v>
+        <v>0.3086247086247087</v>
       </c>
       <c r="R38">
-        <v>0.03333333333333344</v>
+        <v>0.07692307692307687</v>
       </c>
       <c r="S38">
-        <v>30.00000000000004</v>
+        <v>27.00000000000004</v>
       </c>
       <c r="T38">
-        <v>10.1325966850829</v>
+        <v>10.03030303030305</v>
       </c>
       <c r="U38" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>30</v>
       </c>
       <c r="D39">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E39">
         <v>0.25</v>
@@ -2960,31 +2960,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L39">
-        <v>0.3309859154929577</v>
+        <v>0.4123711340206185</v>
       </c>
       <c r="M39">
-        <v>0.7704918032786885</v>
+        <v>0.6557377049180327</v>
       </c>
       <c r="N39">
-        <v>0.4630541871921182</v>
+        <v>0.5063291139240507</v>
       </c>
       <c r="O39">
-        <v>0.08098591549295775</v>
+        <v>0.1623711340206185</v>
       </c>
       <c r="P39">
-        <v>0.7540983606557377</v>
+        <v>0.6393442622950819</v>
       </c>
       <c r="Q39">
-        <v>0.4322849564228875</v>
+        <v>0.47555988315482</v>
       </c>
       <c r="R39">
-        <v>0.323943661971831</v>
+        <v>0.6494845360824741</v>
       </c>
       <c r="S39">
-        <v>46.00000000000005</v>
+        <v>39.00000000000004</v>
       </c>
       <c r="T39">
-        <v>14.04926108374388</v>
+        <v>15.45569620253168</v>
       </c>
       <c r="U39" t="s">
         <v>34</v>
@@ -3001,7 +3001,7 @@
         <v>30</v>
       </c>
       <c r="D40">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E40">
         <v>0.25</v>
@@ -3025,31 +3025,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L40">
-        <v>0.3309859154929577</v>
+        <v>0.4123711340206185</v>
       </c>
       <c r="M40">
-        <v>0.7704918032786885</v>
+        <v>0.6557377049180327</v>
       </c>
       <c r="N40">
-        <v>0.4630541871921182</v>
+        <v>0.5063291139240507</v>
       </c>
       <c r="O40">
-        <v>0.08098591549295775</v>
+        <v>0.1623711340206185</v>
       </c>
       <c r="P40">
-        <v>0.7540983606557377</v>
+        <v>0.6393442622950819</v>
       </c>
       <c r="Q40">
-        <v>0.4322849564228875</v>
+        <v>0.47555988315482</v>
       </c>
       <c r="R40">
-        <v>0.323943661971831</v>
+        <v>0.6494845360824741</v>
       </c>
       <c r="S40">
-        <v>46.00000000000005</v>
+        <v>39.00000000000004</v>
       </c>
       <c r="T40">
-        <v>14.04926108374388</v>
+        <v>15.45569620253168</v>
       </c>
       <c r="U40" t="s">
         <v>34</v>
@@ -3066,7 +3066,7 @@
         <v>30</v>
       </c>
       <c r="D41">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E41">
         <v>0.25</v>
@@ -3090,31 +3090,31 @@
         <v>0.1418604651162791</v>
       </c>
       <c r="L41">
-        <v>0.3309859154929577</v>
+        <v>0.4123711340206185</v>
       </c>
       <c r="M41">
-        <v>0.7704918032786885</v>
+        <v>0.6557377049180327</v>
       </c>
       <c r="N41">
-        <v>0.4630541871921182</v>
+        <v>0.5063291139240507</v>
       </c>
       <c r="O41">
-        <v>0.08098591549295775</v>
+        <v>0.1623711340206185</v>
       </c>
       <c r="P41">
-        <v>0.7540983606557377</v>
+        <v>0.6393442622950819</v>
       </c>
       <c r="Q41">
-        <v>0.4322849564228875</v>
+        <v>0.47555988315482</v>
       </c>
       <c r="R41">
-        <v>0.323943661971831</v>
+        <v>0.6494845360824741</v>
       </c>
       <c r="S41">
-        <v>46.00000000000005</v>
+        <v>39.00000000000004</v>
       </c>
       <c r="T41">
-        <v>14.04926108374388</v>
+        <v>15.45569620253168</v>
       </c>
       <c r="U41" t="s">
         <v>34</v>
